--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/6548-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/6548-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{29AA28BE-E219-484D-9B1F-DEAD42CA2003}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D30EE305-D050-48AA-9319-FA33E9427D68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{4083E6EE-72D0-4811-B5F9-4A492A61B4CF}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{A2E493E9-456A-4DD1-8C97-90C599D0127A}"/>
   </bookViews>
   <sheets>
     <sheet name="6548-dividend-20260225_0_4" sheetId="2" r:id="rId1"/>
@@ -1585,23 +1585,23 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A45E9DA4-909A-4F21-BC81-F82CE8DCEACF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE52A4EC-B960-4B48-891A-8BF0115B090C}">
   <dimension ref="A1:R38"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="8.77734375" customWidth="1"/>
-    <col min="3" max="3" width="8.5546875" customWidth="1"/>
-    <col min="4" max="6" width="8.33203125" customWidth="1"/>
-    <col min="7" max="9" width="8" customWidth="1"/>
-    <col min="10" max="10" width="8.33203125" customWidth="1"/>
-    <col min="11" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="8.33203125" customWidth="1"/>
-    <col min="15" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="8.44140625" customWidth="1"/>
+    <col min="1" max="1" width="6.375" customWidth="1"/>
+    <col min="2" max="2" width="10.875" customWidth="1"/>
+    <col min="3" max="3" width="10.625" customWidth="1"/>
+    <col min="4" max="6" width="10.375" customWidth="1"/>
+    <col min="7" max="9" width="9.875" customWidth="1"/>
+    <col min="10" max="10" width="10.375" customWidth="1"/>
+    <col min="11" max="13" width="9.875" customWidth="1"/>
+    <col min="14" max="14" width="10.375" customWidth="1"/>
+    <col min="15" max="17" width="9.875" customWidth="1"/>
+    <col min="18" max="18" width="11.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
@@ -1629,7 +1629,7 @@
       <c r="Q1" s="32"/>
       <c r="R1" s="24"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="25" t="s">
         <v>1</v>
       </c>
@@ -1659,7 +1659,7 @@
       <c r="Q2" s="34"/>
       <c r="R2" s="35"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="25" t="s">
         <v>2</v>
       </c>
@@ -1705,7 +1705,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="27"/>
       <c r="B4" s="28"/>
       <c r="C4" s="7"/>
@@ -1755,7 +1755,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="39">
         <v>2026</v>
       </c>
@@ -1809,7 +1809,7 @@
         <v>3.62</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="41"/>
       <c r="B6" s="42"/>
       <c r="C6" s="44"/>
@@ -1835,7 +1835,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>27</v>
       </c>
@@ -1891,7 +1891,7 @@
         <v>0.91</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="49">
         <v>2025</v>
       </c>
@@ -1945,7 +1945,7 @@
         <v>3.82</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="19" t="s">
         <v>27</v>
       </c>
@@ -2001,7 +2001,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="19" t="s">
         <v>27</v>
       </c>
@@ -2057,7 +2057,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="19" t="s">
         <v>27</v>
       </c>
@@ -2113,7 +2113,7 @@
         <v>1.42</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="19" t="s">
         <v>27</v>
       </c>
@@ -2169,7 +2169,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="51">
         <v>2024</v>
       </c>
@@ -2223,7 +2223,7 @@
         <v>4.4800000000000004</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
         <v>27</v>
       </c>
@@ -2279,7 +2279,7 @@
         <v>1.21</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
         <v>27</v>
       </c>
@@ -2335,7 +2335,7 @@
         <v>1.07</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
         <v>27</v>
       </c>
@@ -2391,7 +2391,7 @@
         <v>1.02</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
         <v>27</v>
       </c>
@@ -2447,7 +2447,7 @@
         <v>1.18</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="49">
         <v>2023</v>
       </c>
@@ -2501,7 +2501,7 @@
         <v>4.2300000000000004</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="19" t="s">
         <v>27</v>
       </c>
@@ -2557,7 +2557,7 @@
         <v>1.22</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="19" t="s">
         <v>27</v>
       </c>
@@ -2613,7 +2613,7 @@
         <v>1.1499999999999999</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="19" t="s">
         <v>27</v>
       </c>
@@ -2669,7 +2669,7 @@
         <v>1.86</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="51">
         <v>2022</v>
       </c>
@@ -2723,7 +2723,7 @@
         <v>4.1500000000000004</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="11" t="s">
         <v>27</v>
       </c>
@@ -2779,7 +2779,7 @@
         <v>2.19</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="11" t="s">
         <v>27</v>
       </c>
@@ -2835,7 +2835,7 @@
         <v>1.95</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="49">
         <v>2021</v>
       </c>
@@ -2889,7 +2889,7 @@
         <v>2.11</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="19" t="s">
         <v>27</v>
       </c>
@@ -2945,7 +2945,7 @@
         <v>0.68</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="19" t="s">
         <v>27</v>
       </c>
@@ -3001,7 +3001,7 @@
         <v>1.43</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="51">
         <v>2020</v>
       </c>
@@ -3055,7 +3055,7 @@
         <v>3.56</v>
       </c>
     </row>
-    <row r="29" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="11" t="s">
         <v>27</v>
       </c>
@@ -3111,7 +3111,7 @@
         <v>0.72</v>
       </c>
     </row>
-    <row r="30" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="11" t="s">
         <v>27</v>
       </c>
@@ -3167,7 +3167,7 @@
         <v>2.84</v>
       </c>
     </row>
-    <row r="31" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="49">
         <v>2019</v>
       </c>
@@ -3221,7 +3221,7 @@
         <v>7.08</v>
       </c>
     </row>
-    <row r="32" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="19" t="s">
         <v>27</v>
       </c>
@@ -3277,7 +3277,7 @@
         <v>0.99</v>
       </c>
     </row>
-    <row r="33" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="19" t="s">
         <v>27</v>
       </c>
@@ -3333,7 +3333,7 @@
         <v>6.09</v>
       </c>
     </row>
-    <row r="34" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="51">
         <v>2018</v>
       </c>
@@ -3387,7 +3387,7 @@
         <v>2.85</v>
       </c>
     </row>
-    <row r="35" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="49">
         <v>2017</v>
       </c>
@@ -3441,7 +3441,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="36" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="51">
         <v>2016</v>
       </c>
@@ -3495,7 +3495,7 @@
         <v>1.9</v>
       </c>
     </row>
-    <row r="37" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A37" s="49">
         <v>2015</v>
       </c>
@@ -3549,7 +3549,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="38" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A38" s="51" t="s">
         <v>66</v>
       </c>
